--- a/Result/profitability/1595.xlsx
+++ b/Result/profitability/1595.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM68"/>
+  <dimension ref="A1:AM69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.42</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.06250000000000006</v>
+        <v>-0.05750000000000005</v>
       </c>
       <c r="N2" t="n">
-        <v>27.5125</v>
+        <v>27.76625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.86</v>
       </c>
       <c r="M3" t="n">
-        <v>0.205</v>
+        <v>0.16875</v>
       </c>
       <c r="N3" t="n">
-        <v>30.10125</v>
+        <v>29.2725</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4275</v>
+        <v>0.44</v>
       </c>
       <c r="N4" t="n">
-        <v>31.55875</v>
+        <v>31.57</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>3.24</v>
       </c>
       <c r="M5" t="n">
-        <v>0.875</v>
+        <v>0.9775</v>
       </c>
       <c r="N5" t="n">
-        <v>33.91125</v>
+        <v>33.55875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>2.79</v>
       </c>
       <c r="M6" t="n">
-        <v>1.35625</v>
+        <v>1.3775</v>
       </c>
       <c r="N6" t="n">
-        <v>35.3325</v>
+        <v>33.905</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>1.46875</v>
+        <v>1.45625</v>
       </c>
       <c r="N7" t="n">
-        <v>37.1675</v>
+        <v>36.77375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -9064,6 +9064,133 @@
       </c>
       <c r="AM68" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>246</v>
+      </c>
+      <c r="D69" t="n">
+        <v>187</v>
+      </c>
+      <c r="E69" t="n">
+        <v>58</v>
+      </c>
+      <c r="F69" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-27</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-10.81%</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>13</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-13</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-0.395</v>
+      </c>
+      <c r="N69" t="n">
+        <v>25.255</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X69" t="n">
+        <v>-0.6756756756756757</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>9.540000000000001</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.6732533521524349</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>-0.7735849056603774</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>-0.1062947606483227</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
